--- a/AAII_Financials/Quarterly/MCLE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCLE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
   <si>
     <t>MCLE</t>
   </si>
@@ -656,77 +656,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -766,8 +773,14 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,8 +820,14 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,8 +867,14 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,8 +890,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,8 +933,14 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,8 +980,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -988,8 +1027,14 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,8 +1074,14 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,8 +1094,10 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1081,11 +1134,17 @@
       <c r="N17" s="3">
         <v>0</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1122,11 +1181,17 @@
       <c r="N18" s="3">
         <v>0</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,8 +1207,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1180,11 +1247,17 @@
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1221,11 +1294,17 @@
       <c r="N21" s="3">
         <v>0</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1265,8 +1344,14 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1303,11 +1388,17 @@
       <c r="N23" s="3">
         <v>0</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1347,8 +1438,14 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,8 +1485,14 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1426,11 +1529,17 @@
       <c r="N26" s="3">
         <v>0</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1467,11 +1576,17 @@
       <c r="N27" s="3">
         <v>0</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1626,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1525,11 +1646,11 @@
       <c r="F29" s="3">
         <v>0</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -1552,8 +1673,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1720,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,8 +1767,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1672,11 +1811,17 @@
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1713,11 +1858,17 @@
       <c r="N33" s="3">
         <v>0</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,8 +1908,14 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1795,57 +1952,69 @@
       <c r="N35" s="3">
         <v>0</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +2030,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,8 +2049,10 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1898,14 +2071,14 @@
       <c r="H41" s="3">
         <v>0</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
+      <c r="I41" s="3">
+        <v>0</v>
       </c>
       <c r="J41" s="3">
         <v>0</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
+      <c r="K41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L41" s="3">
         <v>0</v>
@@ -1913,14 +2086,20 @@
       <c r="M41" s="3">
         <v>0</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="N41" s="3">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1960,8 +2139,14 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1974,11 +2159,11 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I43" s="3">
         <v>0</v>
@@ -1998,11 +2183,17 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2042,8 +2233,14 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2062,14 +2259,14 @@
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
+      <c r="K45" s="3">
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
@@ -2083,8 +2280,14 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2121,11 +2324,17 @@
       <c r="N46" s="3">
         <v>0</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2165,8 +2374,14 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2206,8 +2421,14 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2220,11 +2441,11 @@
       <c r="F49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -2244,11 +2465,17 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2515,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,8 +2562,14 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2370,8 +2609,14 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,8 +2656,14 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -2449,11 +2700,17 @@
       <c r="N54" s="3">
         <v>0</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3">
+        <v>0</v>
+      </c>
+      <c r="P54" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2726,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,8 +2745,10 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2524,11 +2785,17 @@
       <c r="N57" s="3">
         <v>0</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2568,8 +2835,14 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2606,11 +2879,17 @@
       <c r="N59" s="3">
         <v>0</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2624,14 +2903,14 @@
         <v>0</v>
       </c>
       <c r="G60" s="3">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
         <v>100</v>
       </c>
-      <c r="H60" s="3">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
       <c r="J60" s="3">
         <v>0</v>
       </c>
@@ -2647,11 +2926,17 @@
       <c r="N60" s="3">
         <v>0</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2691,8 +2976,14 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2732,8 +3023,14 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +3070,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +3117,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,13 +3164,19 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E66" s="3">
         <v>0</v>
@@ -2870,14 +3185,14 @@
         <v>0</v>
       </c>
       <c r="G66" s="3">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3">
         <v>100</v>
       </c>
-      <c r="H66" s="3">
-        <v>0</v>
-      </c>
-      <c r="I66" s="3">
-        <v>0</v>
-      </c>
       <c r="J66" s="3">
         <v>0</v>
       </c>
@@ -2893,11 +3208,17 @@
       <c r="N66" s="3">
         <v>0</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3">
+        <v>0</v>
+      </c>
+      <c r="P66" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3234,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3277,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3324,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,8 +3371,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,8 +3418,14 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3104,10 +3451,10 @@
         <v>-100</v>
       </c>
       <c r="K72" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L72" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M72" s="3">
         <v>0</v>
@@ -3115,11 +3462,17 @@
       <c r="N72" s="3">
         <v>0</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3">
+        <v>0</v>
+      </c>
+      <c r="P72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3512,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3559,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,13 +3606,19 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E76" s="3">
         <v>0</v>
@@ -3256,14 +3627,14 @@
         <v>0</v>
       </c>
       <c r="G76" s="3">
+        <v>0</v>
+      </c>
+      <c r="H76" s="3">
+        <v>0</v>
+      </c>
+      <c r="I76" s="3">
         <v>-100</v>
       </c>
-      <c r="H76" s="3">
-        <v>0</v>
-      </c>
-      <c r="I76" s="3">
-        <v>0</v>
-      </c>
       <c r="J76" s="3">
         <v>0</v>
       </c>
@@ -3279,11 +3650,17 @@
       <c r="N76" s="3">
         <v>0</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3">
+        <v>0</v>
+      </c>
+      <c r="P76" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,54 +3700,66 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3407,11 +3796,17 @@
       <c r="N81" s="3">
         <v>0</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,8 +3822,10 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3441,11 +3838,11 @@
       <c r="F83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
@@ -3465,11 +3862,17 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +3912,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +3959,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +4006,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +4053,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,8 +4100,14 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3711,11 +4144,17 @@
       <c r="N89" s="3">
         <v>0</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,8 +4170,10 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3772,8 +4213,14 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4260,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,8 +4307,14 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3895,8 +4354,14 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,8 +4377,10 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3953,8 +4420,14 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4467,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4514,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,8 +4561,14 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4114,11 +4605,17 @@
       <c r="N100" s="3">
         <v>0</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4158,8 +4655,14 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4196,7 +4699,13 @@
       <c r="N102" s="3">
         <v>0</v>
       </c>
-      <c r="O102" s="3" t="s">
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MCLE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCLE_QTR_FIN.xlsx
@@ -656,84 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -779,8 +783,11 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -826,8 +833,11 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -873,8 +883,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,8 +905,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -939,8 +953,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,8 +1003,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1033,8 +1053,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,8 +1122,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1140,11 +1167,14 @@
       <c r="P17" s="3">
         <v>0</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1187,11 +1217,14 @@
       <c r="P18" s="3">
         <v>0</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,8 +1242,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1253,11 +1287,14 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1300,34 +1337,37 @@
       <c r="P21" s="3">
         <v>0</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1350,8 +1390,11 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1394,11 +1437,14 @@
       <c r="P23" s="3">
         <v>0</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1444,8 +1490,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,8 +1540,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1535,11 +1587,14 @@
       <c r="P26" s="3">
         <v>0</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1582,11 +1637,14 @@
       <c r="P27" s="3">
         <v>0</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,8 +1840,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1817,11 +1887,14 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1864,11 +1937,14 @@
       <c r="P33" s="3">
         <v>0</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,8 +1990,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1958,63 +2037,69 @@
       <c r="P35" s="3">
         <v>0</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,8 +2137,9 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2077,11 +2164,11 @@
       <c r="J41" s="3">
         <v>0</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3">
-        <v>0</v>
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M41" s="3">
         <v>0</v>
@@ -2092,14 +2179,17 @@
       <c r="O41" s="3">
         <v>0</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
+      <c r="P41" s="3">
+        <v>0</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2145,25 +2235,28 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
+        <v>0</v>
       </c>
       <c r="I43" s="3">
         <v>0</v>
@@ -2189,11 +2282,14 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2239,37 +2335,40 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
+        <v>0</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
@@ -2286,8 +2385,11 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2330,11 +2432,14 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2380,8 +2485,11 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2427,8 +2535,11 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2447,8 +2558,8 @@
       <c r="H49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -2471,11 +2582,14 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,8 +2685,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2615,8 +2735,11 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,8 +2785,11 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -2706,11 +2832,14 @@
       <c r="P54" s="3">
         <v>0</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3">
+        <v>0</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,8 +2877,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2791,11 +2922,14 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2841,8 +2975,11 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2885,11 +3022,14 @@
       <c r="P59" s="3">
         <v>0</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2909,11 +3049,11 @@
         <v>0</v>
       </c>
       <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3">
         <v>100</v>
       </c>
-      <c r="J60" s="3">
-        <v>0</v>
-      </c>
       <c r="K60" s="3">
         <v>0</v>
       </c>
@@ -2932,16 +3072,19 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -2982,8 +3125,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3029,8 +3175,11 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,8 +3325,11 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3179,7 +3337,7 @@
         <v>100</v>
       </c>
       <c r="E66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F66" s="3">
         <v>0</v>
@@ -3191,11 +3349,11 @@
         <v>0</v>
       </c>
       <c r="I66" s="3">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3">
         <v>100</v>
       </c>
-      <c r="J66" s="3">
-        <v>0</v>
-      </c>
       <c r="K66" s="3">
         <v>0</v>
       </c>
@@ -3214,11 +3372,14 @@
       <c r="P66" s="3">
         <v>0</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3">
+        <v>0</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,8 +3595,11 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3457,7 +3631,7 @@
         <v>-100</v>
       </c>
       <c r="M72" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N72" s="3">
         <v>0</v>
@@ -3468,11 +3642,14 @@
       <c r="P72" s="3">
         <v>0</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3">
+        <v>0</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,8 +3795,11 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -3621,7 +3807,7 @@
         <v>-100</v>
       </c>
       <c r="E76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F76" s="3">
         <v>0</v>
@@ -3633,11 +3819,11 @@
         <v>0</v>
       </c>
       <c r="I76" s="3">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3">
         <v>-100</v>
       </c>
-      <c r="J76" s="3">
-        <v>0</v>
-      </c>
       <c r="K76" s="3">
         <v>0</v>
       </c>
@@ -3656,11 +3842,14 @@
       <c r="P76" s="3">
         <v>0</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3">
+        <v>0</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,60 +3895,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3802,11 +3997,14 @@
       <c r="P81" s="3">
         <v>0</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,8 +4022,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3844,8 +4043,8 @@
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -3868,11 +4067,14 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,8 +4320,11 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4150,11 +4367,14 @@
       <c r="P89" s="3">
         <v>0</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,8 +4392,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4219,8 +4440,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,8 +4540,11 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4360,8 +4590,11 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4612,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,8 +4810,11 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4611,11 +4857,14 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4661,8 +4910,11 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4705,7 +4957,10 @@
       <c r="P102" s="3">
         <v>0</v>
       </c>
-      <c r="Q102" s="3" t="s">
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MCLE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MCLE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>MCLE</t>
   </si>
@@ -656,88 +656,92 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -786,8 +790,11 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -836,8 +843,11 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -886,8 +896,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,8 +919,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -956,8 +970,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,8 +1023,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1056,8 +1076,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1106,8 +1129,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,8 +1149,9 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1170,11 +1197,14 @@
       <c r="Q17" s="3">
         <v>0</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R17" s="3">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1220,11 +1250,14 @@
       <c r="Q18" s="3">
         <v>0</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,8 +1276,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1290,11 +1324,14 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1340,19 +1377,22 @@
       <c r="Q21" s="3">
         <v>0</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
+      <c r="E22" s="3">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
@@ -1369,8 +1409,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1393,8 +1433,11 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1440,11 +1483,14 @@
       <c r="Q23" s="3">
         <v>0</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1493,8 +1539,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,8 +1592,11 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1590,11 +1642,14 @@
       <c r="Q26" s="3">
         <v>0</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1640,11 +1695,14 @@
       <c r="Q27" s="3">
         <v>0</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1751,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1804,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1857,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,8 +1910,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1890,11 +1960,14 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1940,11 +2013,14 @@
       <c r="Q33" s="3">
         <v>0</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,8 +2069,11 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2040,66 +2119,72 @@
       <c r="Q35" s="3">
         <v>0</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2203,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,8 +2224,9 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2167,11 +2254,11 @@
       <c r="K41" s="3">
         <v>0</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3">
-        <v>0</v>
+      <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N41" s="3">
         <v>0</v>
@@ -2182,14 +2269,17 @@
       <c r="P41" s="3">
         <v>0</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
+      <c r="Q41" s="3">
+        <v>0</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2238,8 +2328,11 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2285,11 +2378,14 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2338,8 +2434,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2364,14 +2463,14 @@
       <c r="J45" s="3">
         <v>0</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
+      <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
+        <v>0</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
@@ -2388,8 +2487,11 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2435,11 +2537,14 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2488,8 +2593,11 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2538,28 +2646,31 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -2585,11 +2696,14 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2752,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,8 +2805,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2738,8 +2858,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,8 +2911,11 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -2835,11 +2961,14 @@
       <c r="Q54" s="3">
         <v>0</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3">
+        <v>0</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2987,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,8 +3008,9 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2925,11 +3056,14 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2978,8 +3112,11 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3025,11 +3162,14 @@
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3052,11 +3192,11 @@
         <v>0</v>
       </c>
       <c r="J60" s="3">
+        <v>0</v>
+      </c>
+      <c r="K60" s="3">
         <v>100</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3075,11 +3215,14 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3087,7 +3230,7 @@
         <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -3128,8 +3271,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3178,8 +3324,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3377,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3430,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,8 +3483,11 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3340,7 +3498,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G66" s="3">
         <v>0</v>
@@ -3352,11 +3510,11 @@
         <v>0</v>
       </c>
       <c r="J66" s="3">
+        <v>0</v>
+      </c>
+      <c r="K66" s="3">
         <v>100</v>
       </c>
-      <c r="K66" s="3">
-        <v>0</v>
-      </c>
       <c r="L66" s="3">
         <v>0</v>
       </c>
@@ -3375,11 +3533,14 @@
       <c r="Q66" s="3">
         <v>0</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R66" s="3">
+        <v>0</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3559,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3610,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3663,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3716,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,13 +3769,16 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="E72" s="3">
         <v>-100</v>
@@ -3634,7 +3808,7 @@
         <v>-100</v>
       </c>
       <c r="N72" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O72" s="3">
         <v>0</v>
@@ -3645,11 +3819,14 @@
       <c r="Q72" s="3">
         <v>0</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3">
+        <v>0</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3875,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3928,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,8 +3981,11 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -3810,7 +3996,7 @@
         <v>-100</v>
       </c>
       <c r="F76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G76" s="3">
         <v>0</v>
@@ -3822,11 +4008,11 @@
         <v>0</v>
       </c>
       <c r="J76" s="3">
+        <v>0</v>
+      </c>
+      <c r="K76" s="3">
         <v>-100</v>
       </c>
-      <c r="K76" s="3">
-        <v>0</v>
-      </c>
       <c r="L76" s="3">
         <v>0</v>
       </c>
@@ -3845,11 +4031,14 @@
       <c r="Q76" s="3">
         <v>0</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3">
+        <v>0</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,63 +4087,69 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4000,11 +4195,14 @@
       <c r="Q81" s="3">
         <v>0</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,8 +4221,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4046,8 +4245,8 @@
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -4070,11 +4269,14 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4325,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4378,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4431,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4484,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,8 +4537,11 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4370,11 +4587,14 @@
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,8 +4613,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4443,8 +4664,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4717,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,8 +4770,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4593,8 +4823,11 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +4846,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4663,8 +4897,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4950,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5003,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,8 +5056,11 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4860,11 +5106,14 @@
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4913,8 +5162,11 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4960,7 +5212,10 @@
       <c r="Q102" s="3">
         <v>0</v>
       </c>
-      <c r="R102" s="3" t="s">
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
